--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-27.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.57</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -610,6 +614,506 @@
       </c>
       <c r="T2" t="n">
         <v>34.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Spanish Copa del Rey</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>UD Castellonense x Almeria</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UD Castellonense</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T3" t="n">
+        <v>31.83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>German Cup</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dortmund x Werder Bremen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>2550</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T4" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>English National League North</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Spennymoor Town x South Shields</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Spennymoor Town</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>South Shields</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>42.44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>English National League South</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Walton &amp; Hersham x Salisbury City</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Walton &amp; Hersham</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Salisbury City</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>210</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="T6" t="n">
+        <v>45.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Woking x Boreham Wood</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>913</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>36.73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Spanish Copa del Rey</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Recreativo Huelva x Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recreativo Huelva</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>389</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T8" t="n">
+        <v>35.37</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-27.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-27.xlsx
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.62</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -918,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.65</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1000,15 +1008,19 @@
       <c r="K7" t="n">
         <v>1.57</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1082,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.61</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
